--- a/Baker5/Zero2.xlsx
+++ b/Baker5/Zero2.xlsx
@@ -596,7 +596,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" customHeight="1" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col width="31.6640625" customWidth="1" style="11" min="1" max="1"/>
     <col width="87.1640625" customWidth="1" style="11" min="2" max="2"/>
@@ -1281,7 +1281,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S90"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="42.1640625" customWidth="1" min="1" max="1"/>
   </cols>
@@ -6908,7 +6908,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S90"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="42.1640625" customWidth="1" min="1" max="1"/>
   </cols>

--- a/Baker5/Zero2.xlsx
+++ b/Baker5/Zero2.xlsx
@@ -596,7 +596,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="31.6640625" customWidth="1" style="11" min="1" max="1"/>
     <col width="87.1640625" customWidth="1" style="11" min="2" max="2"/>
@@ -1281,7 +1281,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S90"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelCol="0"/>
   <cols>
     <col width="42.1640625" customWidth="1" min="1" max="1"/>
   </cols>
@@ -6908,7 +6908,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S90"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelCol="0"/>
   <cols>
     <col width="42.1640625" customWidth="1" min="1" max="1"/>
   </cols>
@@ -7089,7 +7089,7 @@
       <c r="F3" s="7" t="n"/>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr">
@@ -7149,7 +7149,7 @@
       <c r="F4" s="7" t="n"/>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
